--- a/NBFC-MF/Borrowers/Bidyabati_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Bidyabati_Daily.xlsx
@@ -8659,140 +8659,148 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="19"/>
-      <c r="B13" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A13" s="19">
+        <v>46277</v>
+      </c>
+      <c r="B13" s="24">
+        <f t="shared" si="3"/>
+        <v>12</v>
       </c>
       <c r="C13" s="20"/>
-      <c r="D13" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E13" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F13" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G13" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H13" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D13" s="21">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="E13" s="21">
+        <f t="shared" si="1"/>
+        <v>86.237818469406491</v>
+      </c>
+      <c r="F13" s="21">
+        <f t="shared" si="5"/>
+        <v>213.76218153059352</v>
+      </c>
+      <c r="G13" s="21">
+        <f t="shared" si="4"/>
+        <v>27478.203145076397</v>
+      </c>
+      <c r="H13" s="21">
+        <f t="shared" si="2"/>
+        <v>2521.796854923603</v>
       </c>
       <c r="J13" s="25" t="s">
         <v>23</v>
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>32700</v>
+        <v>29700</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A14" s="2">
+        <v>46278</v>
+      </c>
+      <c r="B14" s="23">
+        <f t="shared" si="3"/>
+        <v>13</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E14" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F14" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G14" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H14" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D14" s="4">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="E14" s="4">
+        <f t="shared" si="1"/>
+        <v>85.572124142946123</v>
+      </c>
+      <c r="F14" s="4">
+        <f t="shared" si="5"/>
+        <v>214.42787585705389</v>
+      </c>
+      <c r="G14" s="4">
+        <f t="shared" si="4"/>
+        <v>27263.775269219343</v>
+      </c>
+      <c r="H14" s="4">
+        <f t="shared" si="2"/>
+        <v>2736.2247307806574</v>
       </c>
       <c r="J14" s="11" t="s">
         <v>24</v>
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>27691.965326606991</v>
+        <v>25524.137134582503</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="19"/>
-      <c r="B15" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A15" s="19">
+        <v>46279</v>
+      </c>
+      <c r="B15" s="24">
+        <f t="shared" si="3"/>
+        <v>14</v>
       </c>
       <c r="C15" s="20"/>
-      <c r="D15" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E15" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F15" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G15" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H15" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D15" s="21">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="E15" s="21">
+        <f t="shared" si="1"/>
+        <v>84.904356723232723</v>
+      </c>
+      <c r="F15" s="21">
+        <f t="shared" si="5"/>
+        <v>215.09564327676728</v>
+      </c>
+      <c r="G15" s="21">
+        <f t="shared" si="4"/>
+        <v>27048.679625942576</v>
+      </c>
+      <c r="H15" s="21">
+        <f t="shared" si="2"/>
+        <v>2951.3203740574245</v>
       </c>
       <c r="J15" s="13" t="s">
         <v>6</v>
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>2308.0346733930091</v>
+        <v>4475.8628654174972</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A16" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B16" s="23">
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="C16" s="3"/>
-      <c r="D16" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E16" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F16" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G16" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H16" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D16" s="4">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="E16" s="4">
+        <f t="shared" si="1"/>
+        <v>84.234509754276743</v>
+      </c>
+      <c r="F16" s="4">
+        <f t="shared" si="5"/>
+        <v>215.76549024572324</v>
+      </c>
+      <c r="G16" s="4">
+        <f t="shared" si="4"/>
+        <v>26832.914135696854</v>
+      </c>
+      <c r="H16" s="4">
+        <f t="shared" si="2"/>
+        <v>3167.0858643031461</v>
       </c>
       <c r="J16" s="15" t="s">
         <v>18</v>
@@ -8803,31 +8811,33 @@
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="19"/>
-      <c r="B17" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A17" s="19">
+        <v>46281</v>
+      </c>
+      <c r="B17" s="24">
+        <f t="shared" si="3"/>
+        <v>16</v>
       </c>
       <c r="C17" s="20"/>
-      <c r="D17" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E17" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F17" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G17" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H17" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D17" s="21">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="E17" s="21">
+        <f t="shared" si="1"/>
+        <v>83.562576759983443</v>
+      </c>
+      <c r="F17" s="21">
+        <f t="shared" si="5"/>
+        <v>216.43742324001656</v>
+      </c>
+      <c r="G17" s="21">
+        <f t="shared" si="4"/>
+        <v>26616.476712456839</v>
+      </c>
+      <c r="H17" s="21">
+        <f t="shared" si="2"/>
+        <v>3383.5232875431611</v>
       </c>
       <c r="J17" s="17" t="s">
         <v>19</v>
@@ -8838,145 +8848,155 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A18" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B18" s="23">
+        <f t="shared" si="3"/>
+        <v>17</v>
       </c>
       <c r="C18" s="3"/>
-      <c r="D18" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E18" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F18" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G18" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H18" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D18" s="4">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="E18" s="4">
+        <f t="shared" si="1"/>
+        <v>82.888551244090408</v>
+      </c>
+      <c r="F18" s="4">
+        <f t="shared" si="5"/>
+        <v>217.11144875590958</v>
+      </c>
+      <c r="G18" s="4">
+        <f t="shared" si="4"/>
+        <v>26399.365263700929</v>
+      </c>
+      <c r="H18" s="4">
+        <f t="shared" si="2"/>
+        <v>3600.6347362990709</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="19"/>
-      <c r="B19" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A19" s="19">
+        <v>46283</v>
+      </c>
+      <c r="B19" s="24">
+        <f t="shared" si="3"/>
+        <v>18</v>
       </c>
       <c r="C19" s="20"/>
-      <c r="D19" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E19" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F19" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G19" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H19" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D19" s="21">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="E19" s="21">
+        <f t="shared" si="1"/>
+        <v>82.212426690104621</v>
+      </c>
+      <c r="F19" s="21">
+        <f t="shared" si="5"/>
+        <v>217.78757330989538</v>
+      </c>
+      <c r="G19" s="21">
+        <f t="shared" si="4"/>
+        <v>26181.577690391034</v>
+      </c>
+      <c r="H19" s="21">
+        <f t="shared" si="2"/>
+        <v>3818.4223096089663</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A20" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B20" s="23">
+        <f t="shared" si="3"/>
+        <v>19</v>
       </c>
       <c r="C20" s="3"/>
-      <c r="D20" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E20" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F20" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G20" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H20" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D20" s="4">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="E20" s="4">
+        <f t="shared" si="1"/>
+        <v>81.534196561239568</v>
+      </c>
+      <c r="F20" s="4">
+        <f t="shared" si="5"/>
+        <v>218.46580343876042</v>
+      </c>
+      <c r="G20" s="4">
+        <f t="shared" si="4"/>
+        <v>25963.111886952272</v>
+      </c>
+      <c r="H20" s="4">
+        <f t="shared" si="2"/>
+        <v>4036.8881130477275</v>
       </c>
       <c r="J20" s="22"/>
       <c r="K20" s="22"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="19"/>
-      <c r="B21" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A21" s="19">
+        <v>46285</v>
+      </c>
+      <c r="B21" s="24">
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="C21" s="20"/>
-      <c r="D21" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E21" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F21" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G21" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H21" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D21" s="21">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="E21" s="21">
+        <f t="shared" si="1"/>
+        <v>80.853854300351955</v>
+      </c>
+      <c r="F21" s="21">
+        <f t="shared" si="5"/>
+        <v>219.14614569964806</v>
+      </c>
+      <c r="G21" s="21">
+        <f t="shared" si="4"/>
+        <v>25743.965741252625</v>
+      </c>
+      <c r="H21" s="21">
+        <f t="shared" si="2"/>
+        <v>4256.0342587473751</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A22" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B22" s="23">
+        <f t="shared" si="3"/>
+        <v>21</v>
       </c>
       <c r="C22" s="3"/>
-      <c r="D22" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E22" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F22" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G22" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H22" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D22" s="4">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="E22" s="4">
+        <f t="shared" si="1"/>
+        <v>80.171393329878399</v>
+      </c>
+      <c r="F22" s="4">
+        <f t="shared" si="5"/>
+        <v>219.82860667012159</v>
+      </c>
+      <c r="G22" s="4">
+        <f t="shared" si="4"/>
+        <v>25524.137134582503</v>
+      </c>
+      <c r="H22" s="4">
+        <f t="shared" si="2"/>
+        <v>4475.8628654174972</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Bidyabati_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Bidyabati_Daily.xlsx
@@ -8659,7 +8659,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>29700</v>
+        <v>27300</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>25524.137134582503</v>
+        <v>23740.683254256033</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>4475.8628654174972</v>
+        <v>6259.3167457439667</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -9000,227 +9000,243 @@
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="19"/>
-      <c r="B23" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A23" s="19">
+        <v>46287</v>
+      </c>
+      <c r="B23" s="24">
+        <f t="shared" si="3"/>
+        <v>22</v>
       </c>
       <c r="C23" s="20"/>
-      <c r="D23" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E23" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F23" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G23" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H23" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D23" s="21">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="E23" s="21">
+        <f t="shared" si="1"/>
+        <v>79.486807051771748</v>
+      </c>
+      <c r="F23" s="21">
+        <f t="shared" si="5"/>
+        <v>220.51319294822827</v>
+      </c>
+      <c r="G23" s="21">
+        <f t="shared" si="4"/>
+        <v>25303.623941634276</v>
+      </c>
+      <c r="H23" s="21">
+        <f t="shared" si="2"/>
+        <v>4696.376058365724</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="2"/>
-      <c r="B24" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A24" s="2">
+        <v>46288</v>
+      </c>
+      <c r="B24" s="23">
+        <f t="shared" si="3"/>
+        <v>23</v>
       </c>
       <c r="C24" s="3"/>
-      <c r="D24" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E24" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F24" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G24" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H24" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D24" s="4">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="E24" s="4">
+        <f t="shared" si="1"/>
+        <v>78.800088847437323</v>
+      </c>
+      <c r="F24" s="4">
+        <f t="shared" si="5"/>
+        <v>221.19991115256266</v>
+      </c>
+      <c r="G24" s="4">
+        <f t="shared" si="4"/>
+        <v>25082.424030481714</v>
+      </c>
+      <c r="H24" s="4">
+        <f t="shared" si="2"/>
+        <v>4917.575969518286</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="19"/>
-      <c r="B25" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A25" s="19">
+        <v>46288</v>
+      </c>
+      <c r="B25" s="24">
+        <f t="shared" si="3"/>
+        <v>24</v>
       </c>
       <c r="C25" s="20"/>
-      <c r="D25" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E25" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F25" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G25" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H25" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D25" s="21">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="E25" s="21">
+        <f t="shared" si="1"/>
+        <v>78.111232077668987</v>
+      </c>
+      <c r="F25" s="21">
+        <f t="shared" si="5"/>
+        <v>221.888767922331</v>
+      </c>
+      <c r="G25" s="21">
+        <f t="shared" si="4"/>
+        <v>24860.535262559384</v>
+      </c>
+      <c r="H25" s="21">
+        <f t="shared" si="2"/>
+        <v>5139.4647374406159</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="2"/>
-      <c r="B26" s="23" t="str">
+      <c r="A26" s="2">
+        <v>46290</v>
+      </c>
+      <c r="B26" s="23">
         <f>IF(A26&lt;&gt;"",B25+1,"")</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="C26" s="3"/>
-      <c r="D26" s="4" t="str">
+      <c r="D26" s="4">
         <f>IF(AND($A26&lt;&gt;"",$B26&lt;&gt;""),$K$9,"")</f>
-        <v/>
-      </c>
-      <c r="E26" s="4" t="str">
+        <v>300</v>
+      </c>
+      <c r="E26" s="4">
         <f>IF(AND($A26&lt;&gt;"",$B26&lt;&gt;""),G25*$K$8,"")</f>
-        <v/>
-      </c>
-      <c r="F26" s="4" t="str">
+        <v>77.420230082584851</v>
+      </c>
+      <c r="F26" s="4">
         <f>IF(AND($A26&lt;&gt;"",$B26&lt;&gt;""),D26-E26,"")</f>
-        <v/>
-      </c>
-      <c r="G26" s="4" t="str">
+        <v>222.57976991741515</v>
+      </c>
+      <c r="G26" s="4">
         <f>IF(AND($A26&lt;&gt;"",$B26&lt;&gt;""),G25-F26,"")</f>
-        <v/>
-      </c>
-      <c r="H26" s="4" t="str">
+        <v>24637.95549264197</v>
+      </c>
+      <c r="H26" s="4">
         <f>IF(AND($A26&lt;&gt;"",$B26&lt;&gt;""),$K$7-G26,"")</f>
-        <v/>
+        <v>5362.0445073580304</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="19"/>
-      <c r="B27" s="24" t="str">
+      <c r="A27" s="19">
+        <v>46291</v>
+      </c>
+      <c r="B27" s="24">
         <f>IF(A27&lt;&gt;"",B26+1,"")</f>
-        <v/>
+        <v>26</v>
       </c>
       <c r="C27" s="20"/>
-      <c r="D27" s="21" t="str">
+      <c r="D27" s="21">
         <f>IF(AND($A27&lt;&gt;"",$B27&lt;&gt;""),$K$9,"")</f>
-        <v/>
-      </c>
-      <c r="E27" s="21" t="str">
+        <v>300</v>
+      </c>
+      <c r="E27" s="21">
         <f>IF(AND($A27&lt;&gt;"",$B27&lt;&gt;""),G26*$K$8,"")</f>
-        <v/>
-      </c>
-      <c r="F27" s="21" t="str">
+        <v>76.727076181562964</v>
+      </c>
+      <c r="F27" s="21">
         <f>IF(AND($A27&lt;&gt;"",$B27&lt;&gt;""),D27-E27,"")</f>
-        <v/>
-      </c>
-      <c r="G27" s="21" t="str">
+        <v>223.27292381843705</v>
+      </c>
+      <c r="G27" s="21">
         <f>IF(AND($A27&lt;&gt;"",$B27&lt;&gt;""),G26-F27,"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="21" t="str">
+        <v>24414.682568823533</v>
+      </c>
+      <c r="H27" s="21">
         <f>IF(AND($A27&lt;&gt;"",$B27&lt;&gt;""),$K$7-G27,"")</f>
-        <v/>
+        <v>5585.3174311764669</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="2"/>
-      <c r="B28" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A28" s="2">
+        <v>46291</v>
+      </c>
+      <c r="B28" s="23">
+        <f t="shared" si="3"/>
+        <v>27</v>
       </c>
       <c r="C28" s="3"/>
-      <c r="D28" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E28" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F28" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G28" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H28" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D28" s="4">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="E28" s="4">
+        <f t="shared" si="1"/>
+        <v>76.031763673176727</v>
+      </c>
+      <c r="F28" s="4">
+        <f t="shared" si="5"/>
+        <v>223.96823632682327</v>
+      </c>
+      <c r="G28" s="4">
+        <f t="shared" si="4"/>
+        <v>24190.714332496711</v>
+      </c>
+      <c r="H28" s="4">
+        <f t="shared" si="2"/>
+        <v>5809.285667503289</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="19"/>
-      <c r="B29" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A29" s="19">
+        <v>46293</v>
+      </c>
+      <c r="B29" s="24">
+        <f t="shared" si="3"/>
+        <v>28</v>
       </c>
       <c r="C29" s="20"/>
-      <c r="D29" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E29" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F29" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G29" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H29" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D29" s="21">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="E29" s="21">
+        <f t="shared" si="1"/>
+        <v>75.334285835130046</v>
+      </c>
+      <c r="F29" s="21">
+        <f t="shared" si="5"/>
+        <v>224.66571416486994</v>
+      </c>
+      <c r="G29" s="21">
+        <f t="shared" si="4"/>
+        <v>23966.048618331843</v>
+      </c>
+      <c r="H29" s="21">
+        <f t="shared" si="2"/>
+        <v>6033.9513816681574</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="2"/>
-      <c r="B30" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A30" s="2">
+        <v>46294</v>
+      </c>
+      <c r="B30" s="23">
+        <f t="shared" si="3"/>
+        <v>29</v>
       </c>
       <c r="C30" s="3"/>
-      <c r="D30" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E30" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F30" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G30" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H30" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D30" s="4">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="E30" s="4">
+        <f t="shared" si="1"/>
+        <v>74.634635924192381</v>
+      </c>
+      <c r="F30" s="4">
+        <f t="shared" si="5"/>
+        <v>225.36536407580763</v>
+      </c>
+      <c r="G30" s="4">
+        <f t="shared" si="4"/>
+        <v>23740.683254256033</v>
+      </c>
+      <c r="H30" s="4">
+        <f t="shared" si="2"/>
+        <v>6259.3167457439667</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Bidyabati_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Bidyabati_Daily.xlsx
@@ -8659,7 +8659,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>29</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>27300</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>23740.683254256033</v>
+        <v>20746.264682771092</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>6259.3167457439667</v>
+        <v>9253.7353172289077</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -9240,367 +9240,393 @@
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="19"/>
-      <c r="B31" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A31" s="19">
+        <v>46295</v>
+      </c>
+      <c r="B31" s="24">
+        <f t="shared" si="3"/>
+        <v>30</v>
       </c>
       <c r="C31" s="20"/>
-      <c r="D31" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E31" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F31" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G31" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H31" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D31" s="21">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="E31" s="21">
+        <f t="shared" si="1"/>
+        <v>73.932807176133537</v>
+      </c>
+      <c r="F31" s="21">
+        <f t="shared" si="5"/>
+        <v>226.06719282386646</v>
+      </c>
+      <c r="G31" s="21">
+        <f t="shared" si="4"/>
+        <v>23514.616061432167</v>
+      </c>
+      <c r="H31" s="21">
+        <f t="shared" si="2"/>
+        <v>6485.383938567833</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="2"/>
-      <c r="B32" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A32" s="2">
+        <v>46296</v>
+      </c>
+      <c r="B32" s="23">
+        <f t="shared" si="3"/>
+        <v>31</v>
       </c>
       <c r="C32" s="3"/>
-      <c r="D32" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E32" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F32" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G32" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H32" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D32" s="4">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="E32" s="4">
+        <f t="shared" si="1"/>
+        <v>73.228792805658316</v>
+      </c>
+      <c r="F32" s="4">
+        <f t="shared" si="5"/>
+        <v>226.77120719434168</v>
+      </c>
+      <c r="G32" s="4">
+        <f t="shared" si="4"/>
+        <v>23287.844854237825</v>
+      </c>
+      <c r="H32" s="4">
+        <f t="shared" si="2"/>
+        <v>6712.1551457621754</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="19"/>
-      <c r="B33" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A33" s="19">
+        <v>46297</v>
+      </c>
+      <c r="B33" s="24">
+        <f t="shared" si="3"/>
+        <v>32</v>
       </c>
       <c r="C33" s="20"/>
-      <c r="D33" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E33" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F33" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G33" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H33" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D33" s="21">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="E33" s="21">
+        <f t="shared" si="1"/>
+        <v>72.522586006340831</v>
+      </c>
+      <c r="F33" s="21">
+        <f t="shared" si="5"/>
+        <v>227.47741399365918</v>
+      </c>
+      <c r="G33" s="21">
+        <f t="shared" si="4"/>
+        <v>23060.367440244165</v>
+      </c>
+      <c r="H33" s="21">
+        <f t="shared" si="2"/>
+        <v>6939.6325597558352</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="2"/>
-      <c r="B34" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A34" s="2">
+        <v>46298</v>
+      </c>
+      <c r="B34" s="23">
+        <f t="shared" si="3"/>
+        <v>33</v>
       </c>
       <c r="C34" s="3"/>
-      <c r="D34" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E34" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F34" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G34" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H34" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D34" s="4">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="E34" s="4">
+        <f t="shared" si="1"/>
+        <v>71.814179950558767</v>
+      </c>
+      <c r="F34" s="4">
+        <f t="shared" si="5"/>
+        <v>228.18582004944125</v>
+      </c>
+      <c r="G34" s="4">
+        <f t="shared" si="4"/>
+        <v>22832.181620194722</v>
+      </c>
+      <c r="H34" s="4">
+        <f t="shared" si="2"/>
+        <v>7167.8183798052778</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="19"/>
-      <c r="B35" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A35" s="19">
+        <v>46299</v>
+      </c>
+      <c r="B35" s="24">
+        <f t="shared" si="3"/>
+        <v>34</v>
       </c>
       <c r="C35" s="20"/>
-      <c r="D35" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E35" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F35" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G35" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H35" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D35" s="21">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="E35" s="21">
+        <f t="shared" si="1"/>
+        <v>71.103567789427359</v>
+      </c>
+      <c r="F35" s="21">
+        <f t="shared" si="5"/>
+        <v>228.89643221057264</v>
+      </c>
+      <c r="G35" s="21">
+        <f t="shared" si="4"/>
+        <v>22603.285187984151</v>
+      </c>
+      <c r="H35" s="21">
+        <f t="shared" si="2"/>
+        <v>7396.714812015849</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="2"/>
-      <c r="B36" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A36" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B36" s="23">
+        <f t="shared" si="3"/>
+        <v>35</v>
       </c>
       <c r="C36" s="3"/>
-      <c r="D36" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E36" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F36" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G36" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H36" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D36" s="4">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="E36" s="4">
+        <f t="shared" si="1"/>
+        <v>70.390742652733138</v>
+      </c>
+      <c r="F36" s="4">
+        <f t="shared" si="5"/>
+        <v>229.60925734726686</v>
+      </c>
+      <c r="G36" s="4">
+        <f t="shared" si="4"/>
+        <v>22373.675930636884</v>
+      </c>
+      <c r="H36" s="4">
+        <f t="shared" si="2"/>
+        <v>7626.324069363116</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="19"/>
-      <c r="B37" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A37" s="19">
+        <v>46301</v>
+      </c>
+      <c r="B37" s="24">
+        <f t="shared" si="3"/>
+        <v>36</v>
       </c>
       <c r="C37" s="20"/>
-      <c r="D37" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E37" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F37" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G37" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H37" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D37" s="21">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="E37" s="21">
+        <f t="shared" si="1"/>
+        <v>69.675697648867569</v>
+      </c>
+      <c r="F37" s="21">
+        <f t="shared" si="5"/>
+        <v>230.32430235113242</v>
+      </c>
+      <c r="G37" s="21">
+        <f t="shared" si="4"/>
+        <v>22143.351628285753</v>
+      </c>
+      <c r="H37" s="21">
+        <f t="shared" si="2"/>
+        <v>7856.6483717142473</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="2"/>
-      <c r="B38" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A38" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B38" s="23">
+        <f t="shared" si="3"/>
+        <v>37</v>
       </c>
       <c r="C38" s="3"/>
-      <c r="D38" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E38" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F38" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G38" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H38" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D38" s="4">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="E38" s="4">
+        <f t="shared" si="1"/>
+        <v>68.958425864760386</v>
+      </c>
+      <c r="F38" s="4">
+        <f t="shared" si="5"/>
+        <v>231.04157413523961</v>
+      </c>
+      <c r="G38" s="4">
+        <f t="shared" si="4"/>
+        <v>21912.310054150512</v>
+      </c>
+      <c r="H38" s="4">
+        <f t="shared" si="2"/>
+        <v>8087.6899458494881</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="19"/>
-      <c r="B39" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A39" s="19">
+        <v>46303</v>
+      </c>
+      <c r="B39" s="24">
+        <f t="shared" si="3"/>
+        <v>38</v>
       </c>
       <c r="C39" s="20"/>
-      <c r="D39" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E39" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F39" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G39" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H39" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D39" s="21">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="E39" s="21">
+        <f t="shared" si="1"/>
+        <v>68.23892036581276</v>
+      </c>
+      <c r="F39" s="21">
+        <f t="shared" si="5"/>
+        <v>231.76107963418724</v>
+      </c>
+      <c r="G39" s="21">
+        <f t="shared" si="4"/>
+        <v>21680.548974516325</v>
+      </c>
+      <c r="H39" s="21">
+        <f t="shared" si="2"/>
+        <v>8319.451025483675</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="2"/>
-      <c r="B40" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A40" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B40" s="23">
+        <f t="shared" si="3"/>
+        <v>39</v>
       </c>
       <c r="C40" s="3"/>
-      <c r="D40" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E40" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F40" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G40" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H40" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D40" s="4">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="E40" s="4">
+        <f t="shared" si="1"/>
+        <v>67.517174195830265</v>
+      </c>
+      <c r="F40" s="4">
+        <f t="shared" si="5"/>
+        <v>232.48282580416975</v>
+      </c>
+      <c r="G40" s="4">
+        <f t="shared" si="4"/>
+        <v>21448.066148712154</v>
+      </c>
+      <c r="H40" s="4">
+        <f t="shared" si="2"/>
+        <v>8551.9338512878458</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="19"/>
-      <c r="B41" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A41" s="19">
+        <v>46305</v>
+      </c>
+      <c r="B41" s="24">
+        <f t="shared" si="3"/>
+        <v>40</v>
       </c>
       <c r="C41" s="20"/>
-      <c r="D41" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E41" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F41" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G41" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H41" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D41" s="21">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="E41" s="21">
+        <f t="shared" si="1"/>
+        <v>66.793180376955618</v>
+      </c>
+      <c r="F41" s="21">
+        <f t="shared" si="5"/>
+        <v>233.2068196230444</v>
+      </c>
+      <c r="G41" s="21">
+        <f t="shared" si="4"/>
+        <v>21214.859329089111</v>
+      </c>
+      <c r="H41" s="21">
+        <f t="shared" si="2"/>
+        <v>8785.1406709108887</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="2"/>
-      <c r="B42" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A42" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B42" s="23">
+        <f t="shared" si="3"/>
+        <v>41</v>
       </c>
       <c r="C42" s="3"/>
-      <c r="D42" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E42" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F42" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G42" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H42" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D42" s="4">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="E42" s="4">
+        <f t="shared" si="1"/>
+        <v>66.066931909601209</v>
+      </c>
+      <c r="F42" s="4">
+        <f t="shared" si="5"/>
+        <v>233.93306809039879</v>
+      </c>
+      <c r="G42" s="4">
+        <f t="shared" si="4"/>
+        <v>20980.926260998713</v>
+      </c>
+      <c r="H42" s="4">
+        <f t="shared" si="2"/>
+        <v>9019.0737390012873</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="19"/>
-      <c r="B43" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A43" s="19">
+        <v>46307</v>
+      </c>
+      <c r="B43" s="24">
+        <f t="shared" si="3"/>
+        <v>42</v>
       </c>
       <c r="C43" s="20"/>
-      <c r="D43" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E43" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F43" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G43" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H43" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D43" s="21">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="E43" s="21">
+        <f t="shared" si="1"/>
+        <v>65.338421772381452</v>
+      </c>
+      <c r="F43" s="21">
+        <f t="shared" si="5"/>
+        <v>234.66157822761855</v>
+      </c>
+      <c r="G43" s="21">
+        <f t="shared" si="4"/>
+        <v>20746.264682771092</v>
+      </c>
+      <c r="H43" s="21">
+        <f t="shared" si="2"/>
+        <v>9253.7353172289077</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
